--- a/Deliverables/BOM/eSpark_BOM_Oliver_Flst.xlsx
+++ b/Deliverables/BOM/eSpark_BOM_Oliver_Flst.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25629"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\flst\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F342B11D-E0C7-485E-A254-F10EC695E572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -560,7 +559,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
@@ -748,7 +747,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -769,24 +768,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="1" tint="0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14996795556505021"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="29">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -1107,23 +1094,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1191,13 +1167,13 @@
     <xf numFmtId="164" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1216,7 +1192,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1251,21 +1227,6 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1278,6 +1239,33 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1301,93 +1289,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1405,19 +1306,67 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1760,7 +1709,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:S34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1796,15 +1745,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="58"/>
-      <c r="N1" s="58"/>
-      <c r="O1" s="58"/>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="58"/>
-      <c r="R1" s="58"/>
-      <c r="S1" s="59"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="62"/>
+      <c r="Q1" s="62"/>
+      <c r="R1" s="62"/>
+      <c r="S1" s="63"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1814,7 +1763,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="11"/>
-      <c r="F2" s="54" t="s">
+      <c r="F2" s="49" t="s">
         <v>166</v>
       </c>
       <c r="G2" s="12"/>
@@ -1839,7 +1788,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="13"/>
-      <c r="F3" s="55" t="s">
+      <c r="F3" s="50" t="s">
         <v>167</v>
       </c>
       <c r="G3" s="13"/>
@@ -1854,7 +1803,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="60"/>
+      <c r="S3" s="64"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1864,7 +1813,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="13"/>
-      <c r="F4" s="56" t="s">
+      <c r="F4" s="51" t="s">
         <v>167</v>
       </c>
       <c r="G4" s="14"/>
@@ -1879,7 +1828,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="61"/>
+      <c r="S4" s="65"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1889,7 +1838,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="13"/>
-      <c r="F5" s="57" t="s">
+      <c r="F5" s="52" t="s">
         <v>5</v>
       </c>
       <c r="G5" s="15"/>
@@ -1904,7 +1853,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="61"/>
+      <c r="S5" s="65"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1925,7 +1874,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="61"/>
+      <c r="S6" s="65"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1946,7 +1895,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="61"/>
+      <c r="S7" s="65"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1967,7 +1916,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="61"/>
+      <c r="S8" s="65"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1998,7 +1947,7 @@
       <c r="J9" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="K9" s="68" t="s">
+      <c r="K9" s="54" t="s">
         <v>128</v>
       </c>
       <c r="L9" s="30" t="s">
@@ -2013,7 +1962,7 @@
       <c r="O9" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="P9" s="68" t="s">
+      <c r="P9" s="54" t="s">
         <v>161</v>
       </c>
       <c r="Q9" s="30" t="s">
@@ -2032,7 +1981,7 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="66" t="s">
+      <c r="C10" s="53" t="s">
         <v>118</v>
       </c>
       <c r="D10" s="46" t="s">
@@ -2041,22 +1990,22 @@
       <c r="E10" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="69" t="s">
+      <c r="F10" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="G10" s="72" t="s">
+      <c r="G10" s="57" t="s">
         <v>71</v>
       </c>
       <c r="H10" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="I10" s="69" t="s">
+      <c r="I10" s="55" t="s">
         <v>155</v>
       </c>
-      <c r="J10" s="69" t="s">
+      <c r="J10" s="55" t="s">
         <v>132</v>
       </c>
-      <c r="K10" s="72" t="s">
+      <c r="K10" s="57" t="s">
         <v>101</v>
       </c>
       <c r="L10" s="46">
@@ -2066,21 +2015,21 @@
         <f>L10*5</f>
         <v>5</v>
       </c>
-      <c r="N10" s="72">
-        <v>7</v>
-      </c>
-      <c r="O10" s="76" t="s">
+      <c r="N10" s="57">
+        <v>6</v>
+      </c>
+      <c r="O10" s="74" t="s">
         <v>163</v>
       </c>
-      <c r="P10" s="77">
-        <v>0.91790000000000005</v>
-      </c>
-      <c r="Q10" s="53">
-        <f>P10</f>
-        <v>0.91790000000000005</v>
+      <c r="P10" s="75">
+        <v>1.4064000000000001</v>
+      </c>
+      <c r="Q10" s="94">
+        <f>P10*N10</f>
+        <v>8.4384000000000015</v>
       </c>
       <c r="R10" s="48"/>
-      <c r="S10" s="49"/>
+      <c r="S10" s="76"/>
     </row>
     <row r="11" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
@@ -2088,55 +2037,55 @@
         <f t="shared" ref="B11:B31" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="67" t="s">
+      <c r="C11" s="77" t="s">
         <v>118</v>
       </c>
-      <c r="D11" s="50" t="s">
+      <c r="D11" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="51" t="s">
+      <c r="E11" s="79" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="70" t="s">
+      <c r="F11" s="80" t="s">
         <v>168</v>
       </c>
-      <c r="G11" s="73" t="s">
+      <c r="G11" s="81" t="s">
         <v>169</v>
       </c>
-      <c r="H11" s="50" t="s">
+      <c r="H11" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="I11" s="70" t="s">
+      <c r="I11" s="80" t="s">
         <v>155</v>
       </c>
-      <c r="J11" s="70" t="s">
+      <c r="J11" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="K11" s="73" t="s">
+      <c r="K11" s="81" t="s">
         <v>102</v>
       </c>
-      <c r="L11" s="50">
+      <c r="L11" s="78">
         <v>1</v>
       </c>
-      <c r="M11" s="50">
+      <c r="M11" s="78">
         <f t="shared" ref="M11:M32" si="1">L11*5</f>
         <v>5</v>
       </c>
-      <c r="N11" s="73">
-        <v>7</v>
-      </c>
-      <c r="O11" s="78" t="s">
+      <c r="N11" s="81">
+        <v>6</v>
+      </c>
+      <c r="O11" s="82" t="s">
         <v>163</v>
       </c>
-      <c r="P11" s="79">
-        <v>0.43280000000000002</v>
-      </c>
-      <c r="Q11" s="99">
-        <f t="shared" ref="Q11:Q32" si="2">P11</f>
-        <v>0.43280000000000002</v>
-      </c>
-      <c r="R11" s="52"/>
-      <c r="S11" s="52"/>
+      <c r="P11" s="83">
+        <v>0.37390000000000001</v>
+      </c>
+      <c r="Q11" s="94">
+        <f t="shared" ref="Q11:Q32" si="2">P11*N11</f>
+        <v>2.2434000000000003</v>
+      </c>
+      <c r="R11" s="84"/>
+      <c r="S11" s="84"/>
     </row>
     <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
@@ -2144,7 +2093,7 @@
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="66" t="s">
+      <c r="C12" s="53" t="s">
         <v>118</v>
       </c>
       <c r="D12" s="46" t="s">
@@ -2153,22 +2102,22 @@
       <c r="E12" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="69" t="s">
+      <c r="F12" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="G12" s="72" t="s">
+      <c r="G12" s="57" t="s">
         <v>72</v>
       </c>
       <c r="H12" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="I12" s="69" t="s">
+      <c r="I12" s="55" t="s">
         <v>155</v>
       </c>
-      <c r="J12" s="69" t="s">
+      <c r="J12" s="55" t="s">
         <v>134</v>
       </c>
-      <c r="K12" s="72" t="s">
+      <c r="K12" s="57" t="s">
         <v>103</v>
       </c>
       <c r="L12" s="46">
@@ -2178,18 +2127,18 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N12" s="72">
+      <c r="N12" s="57">
         <v>100</v>
       </c>
-      <c r="O12" s="80" t="s">
+      <c r="O12" s="82" t="s">
         <v>163</v>
       </c>
-      <c r="P12" s="81">
-        <v>3.3999999999999998E-3</v>
-      </c>
-      <c r="Q12" s="53">
+      <c r="P12" s="83">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="Q12" s="94">
         <f t="shared" si="2"/>
-        <v>3.3999999999999998E-3</v>
+        <v>0.26</v>
       </c>
       <c r="R12" s="48"/>
       <c r="S12" s="48"/>
@@ -2200,55 +2149,55 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="67" t="s">
+      <c r="C13" s="77" t="s">
         <v>118</v>
       </c>
-      <c r="D13" s="50" t="s">
+      <c r="D13" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="51" t="s">
+      <c r="E13" s="79" t="s">
         <v>34</v>
       </c>
-      <c r="F13" s="70" t="s">
+      <c r="F13" s="80" t="s">
         <v>56</v>
       </c>
-      <c r="G13" s="73" t="s">
+      <c r="G13" s="81" t="s">
         <v>73</v>
       </c>
-      <c r="H13" s="50" t="s">
+      <c r="H13" s="78" t="s">
         <v>87</v>
       </c>
-      <c r="I13" s="70" t="s">
+      <c r="I13" s="80" t="s">
         <v>155</v>
       </c>
-      <c r="J13" s="70" t="s">
+      <c r="J13" s="80" t="s">
         <v>135</v>
       </c>
-      <c r="K13" s="73" t="s">
+      <c r="K13" s="81" t="s">
         <v>104</v>
       </c>
-      <c r="L13" s="50">
+      <c r="L13" s="78">
         <v>2</v>
       </c>
-      <c r="M13" s="50">
+      <c r="M13" s="78">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N13" s="73">
+      <c r="N13" s="81">
         <v>100</v>
       </c>
       <c r="O13" s="82" t="s">
         <v>163</v>
       </c>
-      <c r="P13" s="79">
-        <v>3.3E-3</v>
-      </c>
-      <c r="Q13" s="99">
+      <c r="P13" s="83">
+        <v>2.8E-3</v>
+      </c>
+      <c r="Q13" s="94">
         <f t="shared" si="2"/>
-        <v>3.3E-3</v>
-      </c>
-      <c r="R13" s="52"/>
-      <c r="S13" s="52"/>
+        <v>0.27999999999999997</v>
+      </c>
+      <c r="R13" s="84"/>
+      <c r="S13" s="84"/>
     </row>
     <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
@@ -2256,7 +2205,7 @@
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="66" t="s">
+      <c r="C14" s="53" t="s">
         <v>118</v>
       </c>
       <c r="D14" s="46" t="s">
@@ -2265,22 +2214,22 @@
       <c r="E14" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="F14" s="69" t="s">
+      <c r="F14" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="G14" s="72" t="s">
+      <c r="G14" s="57" t="s">
         <v>74</v>
       </c>
       <c r="H14" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="I14" s="69" t="s">
+      <c r="I14" s="55" t="s">
         <v>155</v>
       </c>
-      <c r="J14" s="69" t="s">
+      <c r="J14" s="55" t="s">
         <v>136</v>
       </c>
-      <c r="K14" s="72" t="s">
+      <c r="K14" s="57" t="s">
         <v>105</v>
       </c>
       <c r="L14" s="46">
@@ -2290,18 +2239,18 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N14" s="72">
-        <v>50</v>
-      </c>
-      <c r="O14" s="80" t="s">
+      <c r="N14" s="57">
+        <v>100</v>
+      </c>
+      <c r="O14" s="82" t="s">
         <v>163</v>
       </c>
-      <c r="P14" s="81">
-        <v>7.1000000000000004E-3</v>
-      </c>
-      <c r="Q14" s="53">
+      <c r="P14" s="83">
+        <v>5.1000000000000004E-3</v>
+      </c>
+      <c r="Q14" s="94">
         <f t="shared" si="2"/>
-        <v>7.1000000000000004E-3</v>
+        <v>0.51</v>
       </c>
       <c r="R14" s="48"/>
       <c r="S14" s="48"/>
@@ -2312,55 +2261,55 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="67" t="s">
+      <c r="C15" s="77" t="s">
         <v>119</v>
       </c>
-      <c r="D15" s="50" t="s">
+      <c r="D15" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="51" t="s">
+      <c r="E15" s="79" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="70" t="s">
+      <c r="F15" s="80" t="s">
         <v>57</v>
       </c>
-      <c r="G15" s="73" t="s">
+      <c r="G15" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="H15" s="50" t="s">
+      <c r="H15" s="78" t="s">
         <v>88</v>
       </c>
-      <c r="I15" s="70" t="s">
+      <c r="I15" s="80" t="s">
         <v>155</v>
       </c>
-      <c r="J15" s="70" t="s">
+      <c r="J15" s="80" t="s">
         <v>137</v>
       </c>
-      <c r="K15" s="73" t="s">
+      <c r="K15" s="81" t="s">
         <v>158</v>
       </c>
-      <c r="L15" s="50">
+      <c r="L15" s="78">
         <v>1</v>
       </c>
-      <c r="M15" s="50">
+      <c r="M15" s="78">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N15" s="73">
+      <c r="N15" s="81">
         <v>10</v>
       </c>
       <c r="O15" s="82" t="s">
         <v>163</v>
       </c>
-      <c r="P15" s="79">
-        <v>4.0599999999999997E-2</v>
-      </c>
-      <c r="Q15" s="99">
+      <c r="P15" s="83">
+        <v>3.9899999999999998E-2</v>
+      </c>
+      <c r="Q15" s="94">
         <f t="shared" si="2"/>
-        <v>4.0599999999999997E-2</v>
-      </c>
-      <c r="R15" s="52"/>
-      <c r="S15" s="52"/>
+        <v>0.39899999999999997</v>
+      </c>
+      <c r="R15" s="84"/>
+      <c r="S15" s="84"/>
     </row>
     <row r="16" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
@@ -2368,7 +2317,7 @@
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="66" t="s">
+      <c r="C16" s="53" t="s">
         <v>120</v>
       </c>
       <c r="D16" s="46" t="s">
@@ -2377,22 +2326,22 @@
       <c r="E16" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="F16" s="69" t="s">
+      <c r="F16" s="55" t="s">
         <v>58</v>
       </c>
-      <c r="G16" s="72" t="s">
+      <c r="G16" s="57" t="s">
         <v>107</v>
       </c>
       <c r="H16" s="46" t="s">
         <v>89</v>
       </c>
-      <c r="I16" s="69" t="s">
+      <c r="I16" s="55" t="s">
         <v>155</v>
       </c>
-      <c r="J16" s="69" t="s">
+      <c r="J16" s="55" t="s">
         <v>138</v>
       </c>
-      <c r="K16" s="72" t="s">
+      <c r="K16" s="57" t="s">
         <v>159</v>
       </c>
       <c r="L16" s="46">
@@ -2402,18 +2351,18 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N16" s="72">
+      <c r="N16" s="57">
         <v>20</v>
       </c>
-      <c r="O16" s="83" t="s">
+      <c r="O16" s="85" t="s">
         <v>163</v>
       </c>
-      <c r="P16" s="84">
-        <v>3.1399999999999997E-2</v>
-      </c>
-      <c r="Q16" s="53">
+      <c r="P16" s="86">
+        <v>2.6100000000000002E-2</v>
+      </c>
+      <c r="Q16" s="94">
         <f t="shared" si="2"/>
-        <v>3.1399999999999997E-2</v>
+        <v>0.52200000000000002</v>
       </c>
       <c r="R16" s="48"/>
       <c r="S16" s="48"/>
@@ -2424,55 +2373,55 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="67" t="s">
+      <c r="C17" s="77" t="s">
         <v>121</v>
       </c>
-      <c r="D17" s="50" t="s">
+      <c r="D17" s="78" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="51" t="s">
+      <c r="E17" s="79" t="s">
         <v>38</v>
       </c>
-      <c r="F17" s="70" t="s">
+      <c r="F17" s="80" t="s">
         <v>168</v>
       </c>
-      <c r="G17" s="73" t="s">
+      <c r="G17" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="H17" s="50" t="s">
+      <c r="H17" s="78" t="s">
         <v>90</v>
       </c>
-      <c r="I17" s="70" t="s">
+      <c r="I17" s="80" t="s">
         <v>155</v>
       </c>
-      <c r="J17" s="70" t="s">
+      <c r="J17" s="80" t="s">
         <v>139</v>
       </c>
-      <c r="K17" s="73" t="s">
+      <c r="K17" s="81" t="s">
         <v>108</v>
       </c>
-      <c r="L17" s="50">
+      <c r="L17" s="78">
         <v>1</v>
       </c>
-      <c r="M17" s="50">
+      <c r="M17" s="78">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N17" s="73">
-        <v>7</v>
+      <c r="N17" s="81">
+        <v>6</v>
       </c>
       <c r="O17" s="85" t="s">
         <v>163</v>
       </c>
       <c r="P17" s="86">
-        <v>0.43280000000000002</v>
-      </c>
-      <c r="Q17" s="99">
+        <v>0.5091</v>
+      </c>
+      <c r="Q17" s="94">
         <f t="shared" si="2"/>
-        <v>0.43280000000000002</v>
-      </c>
-      <c r="R17" s="52"/>
-      <c r="S17" s="52"/>
+        <v>3.0545999999999998</v>
+      </c>
+      <c r="R17" s="84"/>
+      <c r="S17" s="84"/>
     </row>
     <row r="18" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
@@ -2480,7 +2429,7 @@
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="66" t="s">
+      <c r="C18" s="53" t="s">
         <v>121</v>
       </c>
       <c r="D18" s="46" t="s">
@@ -2489,22 +2438,22 @@
       <c r="E18" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="F18" s="69" t="s">
+      <c r="F18" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="G18" s="72" t="s">
+      <c r="G18" s="57" t="s">
         <v>75</v>
       </c>
       <c r="H18" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="I18" s="69" t="s">
+      <c r="I18" s="55" t="s">
         <v>155</v>
       </c>
-      <c r="J18" s="69" t="s">
+      <c r="J18" s="55" t="s">
         <v>140</v>
       </c>
-      <c r="K18" s="72" t="s">
+      <c r="K18" s="57" t="s">
         <v>159</v>
       </c>
       <c r="L18" s="46">
@@ -2514,18 +2463,18 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N18" s="72">
+      <c r="N18" s="57">
         <v>50</v>
       </c>
       <c r="O18" s="87" t="s">
         <v>163</v>
       </c>
-      <c r="P18" s="81">
-        <v>1.5599999999999999E-2</v>
-      </c>
-      <c r="Q18" s="53">
+      <c r="P18" s="83">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="Q18" s="94">
         <f t="shared" si="2"/>
-        <v>1.5599999999999999E-2</v>
+        <v>0.2</v>
       </c>
       <c r="R18" s="48"/>
       <c r="S18" s="48"/>
@@ -2536,55 +2485,55 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="67" t="s">
+      <c r="C19" s="77" t="s">
         <v>120</v>
       </c>
-      <c r="D19" s="50" t="s">
+      <c r="D19" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="E19" s="51" t="s">
+      <c r="E19" s="79" t="s">
         <v>40</v>
       </c>
-      <c r="F19" s="70" t="s">
+      <c r="F19" s="80" t="s">
         <v>61</v>
       </c>
-      <c r="G19" s="100">
+      <c r="G19" s="88">
         <v>61300211121</v>
       </c>
-      <c r="H19" s="50" t="s">
+      <c r="H19" s="78" t="s">
         <v>91</v>
       </c>
-      <c r="I19" s="70" t="s">
+      <c r="I19" s="80" t="s">
         <v>156</v>
       </c>
-      <c r="J19" s="70" t="s">
+      <c r="J19" s="80" t="s">
         <v>141</v>
       </c>
-      <c r="K19" s="73" t="s">
+      <c r="K19" s="81" t="s">
         <v>159</v>
       </c>
-      <c r="L19" s="50">
+      <c r="L19" s="78">
         <v>10</v>
       </c>
-      <c r="M19" s="50">
+      <c r="M19" s="78">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="N19" s="73">
-        <v>100</v>
-      </c>
-      <c r="O19" s="88" t="s">
+      <c r="N19" s="81">
+        <v>50</v>
+      </c>
+      <c r="O19" s="87" t="s">
         <v>163</v>
       </c>
       <c r="P19" s="89">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="Q19" s="99">
+        <v>1.78E-2</v>
+      </c>
+      <c r="Q19" s="94">
         <f t="shared" si="2"/>
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="R19" s="52"/>
-      <c r="S19" s="52"/>
+        <v>0.89</v>
+      </c>
+      <c r="R19" s="84"/>
+      <c r="S19" s="84"/>
     </row>
     <row r="20" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
@@ -2592,7 +2541,7 @@
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="66" t="s">
+      <c r="C20" s="53" t="s">
         <v>122</v>
       </c>
       <c r="D20" s="46" t="s">
@@ -2601,22 +2550,22 @@
       <c r="E20" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="F20" s="69" t="s">
+      <c r="F20" s="55" t="s">
         <v>62</v>
       </c>
-      <c r="G20" s="72" t="s">
+      <c r="G20" s="57" t="s">
         <v>76</v>
       </c>
       <c r="H20" s="46" t="s">
         <v>92</v>
       </c>
-      <c r="I20" s="69" t="s">
+      <c r="I20" s="55" t="s">
         <v>155</v>
       </c>
-      <c r="J20" s="69" t="s">
+      <c r="J20" s="55" t="s">
         <v>142</v>
       </c>
-      <c r="K20" s="72"/>
+      <c r="K20" s="57"/>
       <c r="L20" s="46">
         <v>4</v>
       </c>
@@ -2624,18 +2573,18 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N20" s="72">
-        <v>22</v>
-      </c>
-      <c r="O20" s="80" t="s">
+      <c r="N20" s="57">
+        <v>21</v>
+      </c>
+      <c r="O20" s="82" t="s">
         <v>163</v>
       </c>
-      <c r="P20" s="81">
-        <v>0.3644</v>
-      </c>
-      <c r="Q20" s="53">
+      <c r="P20" s="83">
+        <v>0.34050000000000002</v>
+      </c>
+      <c r="Q20" s="94">
         <f t="shared" si="2"/>
-        <v>0.3644</v>
+        <v>7.150500000000001</v>
       </c>
       <c r="R20" s="48"/>
       <c r="S20" s="48"/>
@@ -2646,55 +2595,55 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="67" t="s">
+      <c r="C21" s="77" t="s">
         <v>123</v>
       </c>
-      <c r="D21" s="50" t="s">
+      <c r="D21" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="E21" s="51" t="s">
+      <c r="E21" s="79" t="s">
         <v>42</v>
       </c>
-      <c r="F21" s="70" t="s">
+      <c r="F21" s="80" t="s">
         <v>63</v>
       </c>
-      <c r="G21" s="73" t="s">
+      <c r="G21" s="81" t="s">
         <v>170</v>
       </c>
-      <c r="H21" s="50" t="s">
+      <c r="H21" s="78" t="s">
         <v>93</v>
       </c>
-      <c r="I21" s="70" t="s">
+      <c r="I21" s="80" t="s">
         <v>155</v>
       </c>
-      <c r="J21" s="70" t="s">
+      <c r="J21" s="80" t="s">
         <v>143</v>
       </c>
-      <c r="K21" s="73" t="s">
+      <c r="K21" s="81" t="s">
         <v>109</v>
       </c>
-      <c r="L21" s="50">
+      <c r="L21" s="78">
         <v>1</v>
       </c>
-      <c r="M21" s="50">
+      <c r="M21" s="78">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N21" s="73">
-        <v>50</v>
+      <c r="N21" s="81">
+        <v>100</v>
       </c>
       <c r="O21" s="85" t="s">
         <v>163</v>
       </c>
       <c r="P21" s="86">
-        <v>4.3E-3</v>
-      </c>
-      <c r="Q21" s="99">
+        <v>3.8E-3</v>
+      </c>
+      <c r="Q21" s="94">
         <f t="shared" si="2"/>
-        <v>4.3E-3</v>
-      </c>
-      <c r="R21" s="52"/>
-      <c r="S21" s="52"/>
+        <v>0.38</v>
+      </c>
+      <c r="R21" s="84"/>
+      <c r="S21" s="84"/>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
@@ -2702,7 +2651,7 @@
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="66" t="s">
+      <c r="C22" s="53" t="s">
         <v>123</v>
       </c>
       <c r="D22" s="46" t="s">
@@ -2711,22 +2660,22 @@
       <c r="E22" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="F22" s="69" t="s">
+      <c r="F22" s="55" t="s">
         <v>63</v>
       </c>
-      <c r="G22" s="72" t="s">
+      <c r="G22" s="57" t="s">
         <v>77</v>
       </c>
       <c r="H22" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="I22" s="69" t="s">
+      <c r="I22" s="55" t="s">
         <v>155</v>
       </c>
-      <c r="J22" s="69" t="s">
+      <c r="J22" s="55" t="s">
         <v>144</v>
       </c>
-      <c r="K22" s="72" t="s">
+      <c r="K22" s="57" t="s">
         <v>110</v>
       </c>
       <c r="L22" s="46">
@@ -2736,18 +2685,18 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N22" s="72">
+      <c r="N22" s="57">
         <v>100</v>
       </c>
-      <c r="O22" s="80" t="s">
+      <c r="O22" s="82" t="s">
         <v>163</v>
       </c>
-      <c r="P22" s="81">
-        <v>1.5E-3</v>
-      </c>
-      <c r="Q22" s="53">
+      <c r="P22" s="83">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q22" s="94">
         <f t="shared" si="2"/>
-        <v>1.5E-3</v>
+        <v>0.13</v>
       </c>
       <c r="R22" s="48"/>
       <c r="S22" s="48"/>
@@ -2758,55 +2707,55 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="67" t="s">
+      <c r="C23" s="77" t="s">
         <v>123</v>
       </c>
-      <c r="D23" s="50" t="s">
+      <c r="D23" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="51" t="s">
+      <c r="E23" s="79" t="s">
         <v>44</v>
       </c>
-      <c r="F23" s="70" t="s">
+      <c r="F23" s="80" t="s">
         <v>64</v>
       </c>
-      <c r="G23" s="73" t="s">
+      <c r="G23" s="81" t="s">
         <v>78</v>
       </c>
-      <c r="H23" s="50" t="s">
+      <c r="H23" s="78" t="s">
         <v>87</v>
       </c>
-      <c r="I23" s="70" t="s">
+      <c r="I23" s="80" t="s">
         <v>155</v>
       </c>
-      <c r="J23" s="70" t="s">
+      <c r="J23" s="80" t="s">
         <v>145</v>
       </c>
-      <c r="K23" s="73" t="s">
+      <c r="K23" s="81" t="s">
         <v>111</v>
       </c>
-      <c r="L23" s="50">
+      <c r="L23" s="78">
         <v>4</v>
       </c>
-      <c r="M23" s="50">
+      <c r="M23" s="78">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N23" s="73">
+      <c r="N23" s="81">
         <v>100</v>
       </c>
       <c r="O23" s="82" t="s">
         <v>163</v>
       </c>
-      <c r="P23" s="79">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q23" s="99">
+      <c r="P23" s="83">
+        <v>1E-3</v>
+      </c>
+      <c r="Q23" s="94">
         <f t="shared" si="2"/>
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="R23" s="52"/>
-      <c r="S23" s="52"/>
+        <v>0.1</v>
+      </c>
+      <c r="R23" s="84"/>
+      <c r="S23" s="84"/>
     </row>
     <row r="24" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
@@ -2814,7 +2763,7 @@
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="66" t="s">
+      <c r="C24" s="53" t="s">
         <v>123</v>
       </c>
       <c r="D24" s="46" t="s">
@@ -2823,22 +2772,22 @@
       <c r="E24" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="F24" s="69" t="s">
+      <c r="F24" s="55" t="s">
         <v>63</v>
       </c>
-      <c r="G24" s="72" t="s">
+      <c r="G24" s="57" t="s">
         <v>79</v>
       </c>
       <c r="H24" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="I24" s="69" t="s">
+      <c r="I24" s="55" t="s">
         <v>155</v>
       </c>
-      <c r="J24" s="69" t="s">
+      <c r="J24" s="55" t="s">
         <v>146</v>
       </c>
-      <c r="K24" s="72" t="s">
+      <c r="K24" s="57" t="s">
         <v>112</v>
       </c>
       <c r="L24" s="46">
@@ -2848,18 +2797,18 @@
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="N24" s="72">
+      <c r="N24" s="57">
         <v>100</v>
       </c>
-      <c r="O24" s="80" t="s">
+      <c r="O24" s="82" t="s">
         <v>163</v>
       </c>
-      <c r="P24" s="81">
-        <v>1.6999999999999999E-3</v>
-      </c>
-      <c r="Q24" s="53">
+      <c r="P24" s="83">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q24" s="94">
         <f t="shared" si="2"/>
-        <v>1.6999999999999999E-3</v>
+        <v>0.12</v>
       </c>
       <c r="R24" s="48"/>
       <c r="S24" s="48"/>
@@ -2870,55 +2819,55 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="67" t="s">
+      <c r="C25" s="77" t="s">
         <v>123</v>
       </c>
-      <c r="D25" s="50" t="s">
+      <c r="D25" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="E25" s="51" t="s">
+      <c r="E25" s="79" t="s">
         <v>46</v>
       </c>
-      <c r="F25" s="70" t="s">
+      <c r="F25" s="80" t="s">
         <v>171</v>
       </c>
-      <c r="G25" s="73" t="s">
+      <c r="G25" s="81" t="s">
         <v>80</v>
       </c>
-      <c r="H25" s="50" t="s">
+      <c r="H25" s="78" t="s">
         <v>87</v>
       </c>
-      <c r="I25" s="70" t="s">
+      <c r="I25" s="80" t="s">
         <v>155</v>
       </c>
-      <c r="J25" s="70" t="s">
+      <c r="J25" s="80" t="s">
         <v>147</v>
       </c>
-      <c r="K25" s="73" t="s">
+      <c r="K25" s="81" t="s">
         <v>113</v>
       </c>
-      <c r="L25" s="50">
+      <c r="L25" s="78">
         <v>5</v>
       </c>
-      <c r="M25" s="50">
+      <c r="M25" s="78">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="N25" s="73">
+      <c r="N25" s="81">
         <v>50</v>
       </c>
       <c r="O25" s="90" t="s">
         <v>163</v>
       </c>
-      <c r="P25" s="79">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Q25" s="99">
+      <c r="P25" s="83">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="Q25" s="94">
         <f t="shared" si="2"/>
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="R25" s="52"/>
-      <c r="S25" s="52"/>
+        <v>0.155</v>
+      </c>
+      <c r="R25" s="84"/>
+      <c r="S25" s="84"/>
     </row>
     <row r="26" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
@@ -2926,7 +2875,7 @@
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="66" t="s">
+      <c r="C26" s="53" t="s">
         <v>123</v>
       </c>
       <c r="D26" s="46" t="s">
@@ -2935,22 +2884,22 @@
       <c r="E26" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="F26" s="69" t="s">
+      <c r="F26" s="55" t="s">
         <v>63</v>
       </c>
-      <c r="G26" s="72" t="s">
+      <c r="G26" s="57" t="s">
         <v>81</v>
       </c>
       <c r="H26" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="I26" s="69" t="s">
+      <c r="I26" s="55" t="s">
         <v>155</v>
       </c>
-      <c r="J26" s="69" t="s">
+      <c r="J26" s="55" t="s">
         <v>148</v>
       </c>
-      <c r="K26" s="72" t="s">
+      <c r="K26" s="57" t="s">
         <v>114</v>
       </c>
       <c r="L26" s="46">
@@ -2960,18 +2909,18 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N26" s="72">
+      <c r="N26" s="57">
         <v>100</v>
       </c>
-      <c r="O26" s="80" t="s">
+      <c r="O26" s="82" t="s">
         <v>163</v>
       </c>
-      <c r="P26" s="81">
-        <v>1.5E-3</v>
-      </c>
-      <c r="Q26" s="53">
+      <c r="P26" s="83">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q26" s="94">
         <f t="shared" si="2"/>
-        <v>1.5E-3</v>
+        <v>0.12</v>
       </c>
       <c r="R26" s="48"/>
       <c r="S26" s="48"/>
@@ -2982,55 +2931,55 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="67" t="s">
+      <c r="C27" s="77" t="s">
         <v>123</v>
       </c>
-      <c r="D27" s="50" t="s">
+      <c r="D27" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="E27" s="51" t="s">
+      <c r="E27" s="79" t="s">
         <v>48</v>
       </c>
-      <c r="F27" s="70" t="s">
+      <c r="F27" s="80" t="s">
         <v>63</v>
       </c>
-      <c r="G27" s="73" t="s">
+      <c r="G27" s="81" t="s">
         <v>172</v>
       </c>
-      <c r="H27" s="50" t="s">
+      <c r="H27" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="I27" s="70" t="s">
+      <c r="I27" s="80" t="s">
         <v>155</v>
       </c>
-      <c r="J27" s="70" t="s">
+      <c r="J27" s="80" t="s">
         <v>149</v>
       </c>
-      <c r="K27" s="73" t="s">
+      <c r="K27" s="81" t="s">
         <v>115</v>
       </c>
-      <c r="L27" s="50">
+      <c r="L27" s="78">
         <v>1</v>
       </c>
-      <c r="M27" s="50">
+      <c r="M27" s="78">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N27" s="73">
+      <c r="N27" s="81">
         <v>100</v>
       </c>
-      <c r="O27" s="88" t="s">
+      <c r="O27" s="87" t="s">
         <v>163</v>
       </c>
       <c r="P27" s="91">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Q27" s="99">
+        <v>1E-3</v>
+      </c>
+      <c r="Q27" s="94">
         <f t="shared" si="2"/>
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="R27" s="52"/>
-      <c r="S27" s="52"/>
+        <v>0.1</v>
+      </c>
+      <c r="R27" s="84"/>
+      <c r="S27" s="84"/>
     </row>
     <row r="28" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
@@ -3038,7 +2987,7 @@
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="66" t="s">
+      <c r="C28" s="53" t="s">
         <v>124</v>
       </c>
       <c r="D28" s="46" t="s">
@@ -3047,22 +2996,22 @@
       <c r="E28" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="F28" s="69" t="s">
+      <c r="F28" s="55" t="s">
         <v>168</v>
       </c>
-      <c r="G28" s="72" t="s">
+      <c r="G28" s="57" t="s">
         <v>65</v>
       </c>
       <c r="H28" s="46" t="s">
         <v>96</v>
       </c>
-      <c r="I28" s="69" t="s">
+      <c r="I28" s="55" t="s">
         <v>155</v>
       </c>
-      <c r="J28" s="69" t="s">
+      <c r="J28" s="55" t="s">
         <v>150</v>
       </c>
-      <c r="K28" s="72" t="s">
+      <c r="K28" s="57" t="s">
         <v>158</v>
       </c>
       <c r="L28" s="46">
@@ -3072,18 +3021,18 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N28" s="72">
+      <c r="N28" s="57">
         <v>10</v>
       </c>
       <c r="O28" s="87" t="s">
         <v>163</v>
       </c>
-      <c r="P28" s="92">
-        <v>5.91E-2</v>
-      </c>
-      <c r="Q28" s="53">
+      <c r="P28" s="91">
+        <v>5.6300000000000003E-2</v>
+      </c>
+      <c r="Q28" s="94">
         <f t="shared" si="2"/>
-        <v>5.91E-2</v>
+        <v>0.56300000000000006</v>
       </c>
       <c r="R28" s="48"/>
       <c r="S28" s="48"/>
@@ -3094,55 +3043,55 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="67" t="s">
+      <c r="C29" s="77" t="s">
         <v>125</v>
       </c>
-      <c r="D29" s="50" t="s">
+      <c r="D29" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="E29" s="51" t="s">
+      <c r="E29" s="79" t="s">
         <v>50</v>
       </c>
-      <c r="F29" s="70" t="s">
+      <c r="F29" s="80" t="s">
         <v>66</v>
       </c>
-      <c r="G29" s="73" t="s">
+      <c r="G29" s="81" t="s">
         <v>82</v>
       </c>
-      <c r="H29" s="50" t="s">
+      <c r="H29" s="78" t="s">
         <v>97</v>
       </c>
-      <c r="I29" s="70" t="s">
+      <c r="I29" s="80" t="s">
         <v>155</v>
       </c>
-      <c r="J29" s="70" t="s">
+      <c r="J29" s="80" t="s">
         <v>151</v>
       </c>
-      <c r="K29" s="73" t="s">
+      <c r="K29" s="81" t="s">
         <v>158</v>
       </c>
-      <c r="L29" s="50">
+      <c r="L29" s="78">
         <v>1</v>
       </c>
-      <c r="M29" s="50">
+      <c r="M29" s="78">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N29" s="73">
-        <v>6</v>
+      <c r="N29" s="81">
+        <v>10</v>
       </c>
       <c r="O29" s="82" t="s">
         <v>163</v>
       </c>
-      <c r="P29" s="79">
-        <v>0.49409999999999998</v>
-      </c>
-      <c r="Q29" s="99">
+      <c r="P29" s="83">
+        <v>0.36370000000000002</v>
+      </c>
+      <c r="Q29" s="94">
         <f t="shared" si="2"/>
-        <v>0.49409999999999998</v>
-      </c>
-      <c r="R29" s="52"/>
-      <c r="S29" s="52"/>
+        <v>3.6370000000000005</v>
+      </c>
+      <c r="R29" s="84"/>
+      <c r="S29" s="84"/>
     </row>
     <row r="30" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
@@ -3150,7 +3099,7 @@
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="66" t="s">
+      <c r="C30" s="53" t="s">
         <v>125</v>
       </c>
       <c r="D30" s="46" t="s">
@@ -3159,22 +3108,22 @@
       <c r="E30" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="F30" s="69" t="s">
+      <c r="F30" s="55" t="s">
         <v>67</v>
       </c>
-      <c r="G30" s="72" t="s">
+      <c r="G30" s="57" t="s">
         <v>83</v>
       </c>
       <c r="H30" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="I30" s="69" t="s">
+      <c r="I30" s="55" t="s">
         <v>155</v>
       </c>
-      <c r="J30" s="69" t="s">
+      <c r="J30" s="55" t="s">
         <v>152</v>
       </c>
-      <c r="K30" s="72" t="s">
+      <c r="K30" s="57" t="s">
         <v>158</v>
       </c>
       <c r="L30" s="46">
@@ -3184,18 +3133,18 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N30" s="72">
+      <c r="N30" s="57">
         <v>6</v>
       </c>
-      <c r="O30" s="80" t="s">
+      <c r="O30" s="82" t="s">
         <v>163</v>
       </c>
-      <c r="P30" s="81">
-        <v>1.9494</v>
-      </c>
-      <c r="Q30" s="53">
+      <c r="P30" s="83">
+        <v>1.1295999999999999</v>
+      </c>
+      <c r="Q30" s="94">
         <f t="shared" si="2"/>
-        <v>1.9494</v>
+        <v>6.7775999999999996</v>
       </c>
       <c r="R30" s="48"/>
       <c r="S30" s="48"/>
@@ -3206,55 +3155,55 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="67" t="s">
+      <c r="C31" s="77" t="s">
         <v>125</v>
       </c>
-      <c r="D31" s="50" t="s">
+      <c r="D31" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="E31" s="51" t="s">
+      <c r="E31" s="79" t="s">
         <v>52</v>
       </c>
-      <c r="F31" s="70" t="s">
+      <c r="F31" s="80" t="s">
         <v>173</v>
       </c>
-      <c r="G31" s="73" t="s">
+      <c r="G31" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="H31" s="50" t="s">
+      <c r="H31" s="78" t="s">
         <v>99</v>
       </c>
-      <c r="I31" s="70" t="s">
+      <c r="I31" s="80" t="s">
         <v>155</v>
       </c>
-      <c r="J31" s="70" t="s">
+      <c r="J31" s="80" t="s">
         <v>153</v>
       </c>
-      <c r="K31" s="73" t="s">
+      <c r="K31" s="81" t="s">
         <v>158</v>
       </c>
-      <c r="L31" s="50">
+      <c r="L31" s="78">
         <v>1</v>
       </c>
-      <c r="M31" s="50">
+      <c r="M31" s="78">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N31" s="73">
+      <c r="N31" s="81">
         <v>6</v>
       </c>
       <c r="O31" s="82" t="s">
         <v>163</v>
       </c>
-      <c r="P31" s="79">
-        <v>0.94679999999999997</v>
-      </c>
-      <c r="Q31" s="99">
+      <c r="P31" s="83">
+        <v>0.47889999999999999</v>
+      </c>
+      <c r="Q31" s="94">
         <f t="shared" si="2"/>
-        <v>0.94679999999999997</v>
-      </c>
-      <c r="R31" s="52"/>
-      <c r="S31" s="52"/>
+        <v>2.8734000000000002</v>
+      </c>
+      <c r="R31" s="84"/>
+      <c r="S31" s="84"/>
     </row>
     <row r="32" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
@@ -3262,7 +3211,7 @@
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="66" t="s">
+      <c r="C32" s="53" t="s">
         <v>125</v>
       </c>
       <c r="D32" s="46" t="s">
@@ -3271,43 +3220,43 @@
       <c r="E32" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="F32" s="71" t="s">
+      <c r="F32" s="56" t="s">
         <v>174</v>
       </c>
-      <c r="G32" s="74" t="s">
+      <c r="G32" s="58" t="s">
         <v>69</v>
       </c>
       <c r="H32" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="I32" s="71" t="s">
+      <c r="I32" s="56" t="s">
         <v>155</v>
       </c>
-      <c r="J32" s="71" t="s">
+      <c r="J32" s="56" t="s">
         <v>154</v>
       </c>
-      <c r="K32" s="74" t="s">
+      <c r="K32" s="58" t="s">
         <v>158</v>
       </c>
-      <c r="L32" s="75">
+      <c r="L32" s="59">
         <v>1</v>
       </c>
       <c r="M32" s="46">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N32" s="74">
-        <v>6</v>
-      </c>
-      <c r="O32" s="93" t="s">
+      <c r="N32" s="58">
+        <v>10</v>
+      </c>
+      <c r="O32" s="92" t="s">
         <v>163</v>
       </c>
-      <c r="P32" s="94">
-        <v>0.54279999999999995</v>
-      </c>
-      <c r="Q32" s="101">
+      <c r="P32" s="93">
+        <v>0.41510000000000002</v>
+      </c>
+      <c r="Q32" s="94">
         <f t="shared" si="2"/>
-        <v>0.54279999999999995</v>
+        <v>4.1509999999999998</v>
       </c>
       <c r="R32" s="48"/>
       <c r="S32" s="48"/>
@@ -3326,17 +3275,17 @@
       <c r="K33" s="37"/>
       <c r="L33" s="37"/>
       <c r="M33" s="37"/>
-      <c r="N33" s="95" t="s">
+      <c r="N33" s="70" t="s">
         <v>164</v>
       </c>
-      <c r="O33" s="96"/>
-      <c r="P33" s="96"/>
-      <c r="Q33" s="103">
+      <c r="O33" s="71"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="61">
         <f>SUM(Q10:Q32)</f>
-        <v>6.2633000000000001</v>
-      </c>
-      <c r="R33" s="62"/>
-      <c r="S33" s="63"/>
+        <v>43.054900000000004</v>
+      </c>
+      <c r="R33" s="66"/>
+      <c r="S33" s="67"/>
     </row>
     <row r="34" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
@@ -3352,17 +3301,17 @@
       <c r="K34" s="10"/>
       <c r="L34" s="10"/>
       <c r="M34" s="10"/>
-      <c r="N34" s="97" t="s">
+      <c r="N34" s="72" t="s">
         <v>165</v>
       </c>
-      <c r="O34" s="98"/>
-      <c r="P34" s="98"/>
-      <c r="Q34" s="102">
+      <c r="O34" s="73"/>
+      <c r="P34" s="73"/>
+      <c r="Q34" s="60">
         <f>Q33/5</f>
-        <v>1.2526600000000001</v>
-      </c>
-      <c r="R34" s="64"/>
-      <c r="S34" s="65"/>
+        <v>8.6109800000000014</v>
+      </c>
+      <c r="R34" s="68"/>
+      <c r="S34" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3373,29 +3322,29 @@
     <mergeCell ref="N34:P34"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O10" r:id="rId1" xr:uid="{79C24EDB-6696-4985-A0AA-9B47EDFEE46C}"/>
-    <hyperlink ref="O11" r:id="rId2" xr:uid="{80A88D9E-9DEB-4F12-84A3-F2D73F5CA58D}"/>
-    <hyperlink ref="O12" r:id="rId3" xr:uid="{A71CEEAE-F118-48C7-AB73-FF54FD0D0AE8}"/>
-    <hyperlink ref="O13" r:id="rId4" xr:uid="{34810746-7110-4B76-B296-B98202520FE4}"/>
-    <hyperlink ref="O14" r:id="rId5" xr:uid="{410E0719-3A41-440D-A3CD-BF0BC8246C6D}"/>
-    <hyperlink ref="O15" r:id="rId6" xr:uid="{B7CEC3A8-B3CD-4D22-8F03-3EE770AED640}"/>
-    <hyperlink ref="O16" r:id="rId7" xr:uid="{F493CDD7-423B-4369-85B2-17F21D65341F}"/>
-    <hyperlink ref="O17" r:id="rId8" xr:uid="{1714E4BD-B9FD-4E22-932E-8EF587CA1124}"/>
-    <hyperlink ref="O18" r:id="rId9" xr:uid="{215B7125-5A0B-49AC-A9F8-986C452A32E3}"/>
-    <hyperlink ref="O19" r:id="rId10" xr:uid="{8C0B6CEE-1B25-49B8-9611-0FF833C52AB0}"/>
-    <hyperlink ref="O20" r:id="rId11" xr:uid="{135A2093-1808-45E1-AFB8-863076918EF5}"/>
-    <hyperlink ref="O21" r:id="rId12" xr:uid="{B6929841-CEB3-4F82-871E-CCCA6DC311B2}"/>
-    <hyperlink ref="O22" r:id="rId13" xr:uid="{068CF0C1-2459-4326-8F59-9CBC4BACA605}"/>
-    <hyperlink ref="O23" r:id="rId14" xr:uid="{7537A3E5-441B-4901-B776-12C4685742B4}"/>
-    <hyperlink ref="O24" r:id="rId15" xr:uid="{72496619-85D5-4F3E-A042-E07220B8004E}"/>
-    <hyperlink ref="O26" r:id="rId16" xr:uid="{4183A110-0596-46BA-95A3-250A155EDAFA}"/>
-    <hyperlink ref="O27" r:id="rId17" xr:uid="{F1D90B0D-F8C7-4A32-BAE1-94B229761F69}"/>
-    <hyperlink ref="O28" r:id="rId18" xr:uid="{3CF74D61-247A-42E5-B8B2-176990421560}"/>
-    <hyperlink ref="O29" r:id="rId19" xr:uid="{B9726D98-3676-4841-A572-27B8C528E9A8}"/>
-    <hyperlink ref="O30" r:id="rId20" xr:uid="{91329B3A-A953-4DC6-8EC0-591A02842392}"/>
-    <hyperlink ref="O31" r:id="rId21" xr:uid="{24380496-6201-4812-ABE3-6B0EA7204262}"/>
-    <hyperlink ref="O32" r:id="rId22" xr:uid="{FC805A80-A79B-4288-9AA7-4AA2717AB295}"/>
-    <hyperlink ref="O25" r:id="rId23" xr:uid="{061B813A-67BF-43CA-93FF-4142C33C9E45}"/>
+    <hyperlink ref="O10" r:id="rId1"/>
+    <hyperlink ref="O11" r:id="rId2"/>
+    <hyperlink ref="O12" r:id="rId3"/>
+    <hyperlink ref="O13" r:id="rId4"/>
+    <hyperlink ref="O14" r:id="rId5"/>
+    <hyperlink ref="O15" r:id="rId6"/>
+    <hyperlink ref="O16" r:id="rId7"/>
+    <hyperlink ref="O17" r:id="rId8"/>
+    <hyperlink ref="O18" r:id="rId9"/>
+    <hyperlink ref="O19" r:id="rId10"/>
+    <hyperlink ref="O20" r:id="rId11"/>
+    <hyperlink ref="O21" r:id="rId12"/>
+    <hyperlink ref="O22" r:id="rId13"/>
+    <hyperlink ref="O23" r:id="rId14"/>
+    <hyperlink ref="O24" r:id="rId15"/>
+    <hyperlink ref="O26" r:id="rId16"/>
+    <hyperlink ref="O27" r:id="rId17"/>
+    <hyperlink ref="O28" r:id="rId18"/>
+    <hyperlink ref="O29" r:id="rId19"/>
+    <hyperlink ref="O30" r:id="rId20"/>
+    <hyperlink ref="O31" r:id="rId21"/>
+    <hyperlink ref="O32" r:id="rId22"/>
+    <hyperlink ref="O25" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId24"/>
